--- a/e2e/expectedData/moju_CUTAH_Semester_1.xlsx
+++ b/e2e/expectedData/moju_CUTAH_Semester_1.xlsx
@@ -89,7 +89,7 @@
     <t>TOTAL</t>
   </si>
   <si>
-    <t>DILI, 26 Agustus 2026</t>
+    <t>DILI, 09 September 2026</t>
   </si>
   <si>
     <t>PREPARED BY</t>

--- a/e2e/expectedData/moju_CUTAH_Semester_1.xlsx
+++ b/e2e/expectedData/moju_CUTAH_Semester_1.xlsx
@@ -89,7 +89,7 @@
     <t>TOTAL</t>
   </si>
   <si>
-    <t>DILI, 09 September 2026</t>
+    <t>DILI, 10 September 2026</t>
   </si>
   <si>
     <t>PREPARED BY</t>
